--- a/集训文件2/附件5_静态任务数据.xlsx
+++ b/集训文件2/附件5_静态任务数据.xlsx
@@ -138,6 +138,54 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing_wm1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6800000" y="6400000"/>
+    <xdr:ext cx="2200000" cy="350000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2200000" cy="350000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" rtlCol="0" anchor="b" lIns="0" tIns="0" rIns="0" bIns="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="SimSun"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1370,5 +1418,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>